--- a/workbooks/Public_Diplomacy_Learning_Workshop_EN.xlsx
+++ b/workbooks/Public_Diplomacy_Learning_Workshop_EN.xlsx
@@ -26,22 +26,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="266">
   <si>
-    <t xml:space="preserve">Public diplomacy: first steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Find the row for your current week. Click “Open lecture notes”.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Complete the small task. Prepare a short answer using the “Your output” column.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Select your status in the yellow cell. Then read the example on sheet 2 and complete your own evidence row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everyday analogy: Seeing a poster does not mean liking or buying the product it promotes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel tip: Click a yellow cell, type and press Enter. Use the tabs below to move between sheets.</t>
+    <t xml:space="preserve">Public diplomacy: weekly study guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Locate the relevant week. Select “Open lecture notes” to access the assigned reading.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Complete the exercise. Prepare a concise response in the form specified under “Expected output”.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Record progress in the yellow status cell. Review the example on sheet 2, then complete an evidence row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative analogy: Exposure to a poster does not by itself establish approval or purchase of the advertised product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workbook instructions: Select a yellow cell, enter a value and press Enter. Use the tabs below to navigate between sheets.</t>
   </si>
   <si>
     <t xml:space="preserve">Week</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">Topic</t>
   </si>
   <si>
-    <t xml:space="preserve">Small task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your output</t>
+    <t xml:space="preserve">Exercise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected output</t>
   </si>
   <si>
     <t xml:space="preserve">Lecture notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Status (you select)</t>
+    <t xml:space="preserve">Progress status</t>
   </si>
   <si>
     <t xml:space="preserve">Distinguishing types of power</t>
   </si>
   <si>
-    <t xml:space="preserve">Choose a scholarship example. Separate funding, attraction and the expected outcome.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three sentences: What is the resource, what is the instrument, and what evidence of an outcome is missing?</t>
+    <t xml:space="preserve">Select a scholarship example. Distinguish funding, attraction and the expected outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three sentences identifying the resource, instrument and additional evidence required to assess the outcome.</t>
   </si>
   <si>
     <t xml:space="preserve">Not started</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">Franklin and France</t>
   </si>
   <si>
-    <t xml:space="preserve">Choose one of Franklin’s contacts in a scientific or social network. Separate the contact from the alliance decision.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two explanations: How might the contact contribute, and what else might explain the decision?</t>
+    <t xml:space="preserve">Select one of Franklin’s contacts in a scientific or social network. Distinguish this contact from the alliance decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two explanations addressing the contact’s possible contribution and an alternative cause of the decision.</t>
   </si>
   <si>
     <t xml:space="preserve">The Union and Europe</t>
   </si>
   <si>
-    <t xml:space="preserve">Find a narrative used by the Union government. Identify the European audience it addressed.</t>
+    <t xml:space="preserve">Identify a narrative used by the Union government and the European audience it addressed.</t>
   </si>
   <si>
     <t xml:space="preserve">One message, one audience and one type of document that could reveal reception.</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">Explain why cotton as a resource did not automatically produce political support.</t>
   </si>
   <si>
-    <t xml:space="preserve">One resource, one expected outcome and two conditions that might interrupt the chain.</t>
+    <t xml:space="preserve">One resource, one expected outcome and two conditions that might interrupt the proposed process.</t>
   </si>
   <si>
     <t xml:space="preserve">Cuba and humanitarian aid</t>
   </si>
   <si>
-    <t xml:space="preserve">Separate the delivery of aid from media accounts of that aid.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One piece of activity evidence, one piece of reporting evidence and one missing piece of influence evidence.</t>
+    <t xml:space="preserve">Distinguish the delivery of aid from its representation in media accounts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One item of evidence for the activity, one for its reporting and one additional item needed to assess influence.</t>
   </si>
   <si>
     <t xml:space="preserve">Educational exchanges</t>
   </si>
   <si>
-    <t xml:space="preserve">In a student exchange, identify what the host and the participant each learn.</t>
+    <t xml:space="preserve">Identify the learning experiences of the host and participant in a student exchange.</t>
   </si>
   <si>
     <t xml:space="preserve">One indicator of relationships to track alongside participation numbers.</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">The CPI and communication networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Map the Committee on Public Information (CPI) into three boxes: centre, intermediary and audience.</t>
+    <t xml:space="preserve">Represent the communication network of the Committee on Public Information (CPI) in three boxes: centre, intermediary and audience.</t>
   </si>
   <si>
     <t xml:space="preserve">One missing step between producing a poster and persuading a person.</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Foundations and private networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Choose a foundation or university example. Separate who provides funding from who makes decisions.</t>
+    <t xml:space="preserve">Select a foundation or university example. Distinguish funding providers from decision-makers.</t>
   </si>
   <si>
     <t xml:space="preserve">Two actors and one area in which they may act independently.</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">Compare the three institutions in the notes by purpose, intended audience and instruments.</t>
   </si>
   <si>
-    <t xml:space="preserve">Three short rows. Explain why using the same instrument does not imply the same mandate.</t>
+    <t xml:space="preserve">Three concise comparison rows explaining why use of the same instrument does not imply an identical mandate.</t>
   </si>
   <si>
     <t xml:space="preserve">Radio, film and the press</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">Cross-country comparison</t>
   </si>
   <si>
-    <t xml:space="preserve">Compare two cultural institutions or broadcasters: Who governs them, whom do they reach, and how do they receive feedback?</t>
+    <t xml:space="preserve">Compare two cultural institutions or broadcasters in terms of governance, audiences reached and feedback processes.</t>
   </si>
   <si>
     <t xml:space="preserve">A two-row comparison and one contextual difference that might affect the outcome.</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">Evaluating influence</t>
   </si>
   <si>
-    <t xml:space="preserve">Change one yellow input on sheet 3. Read reach and the change in support separately.</t>
+    <t xml:space="preserve">Change one yellow input on sheet 3. Interpret reach and the change in support separately.</t>
   </si>
   <si>
     <t xml:space="preserve">Four sentences: purpose, observation, a rival explanation and further evidence needed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sentence template: “This source shows … . To conclude … , I also need … .”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: “The poster shows that the message was produced. To establish persuasion, I also need audience responses.”</t>
+    <t xml:space="preserve">Analytical sentence template: “This source indicates … . The conclusion that … requires additional evidence of … .”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: “The poster establishes that the message was produced. Assessing persuasion also requires evidence of audience responses.”</t>
   </si>
   <si>
     <t xml:space="preserve">Source: The 14 weeks of English lecture notes on this site. Each weekly row links to the corresponding notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">How do I test a claim against evidence?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. State your claim in one sentence. 2. Identify your document. 3. State what the document cannot establish.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence is a trace supporting a claim. An evidence matrix compares such traces using the same questions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everyday example: Seeing a café advert does not prove that you bought coffee there. Identify the missing step.</t>
+    <t xml:space="preserve">Testing claims against evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. State the claim in one sentence. 2. Identify the document. 3. Specify the limits of what it can establish.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence is a trace supporting a claim. The evidence matrix below compares these traces using a common set of questions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative example: Exposure to a café advertisement does not establish a purchase. Identify the missing step between the two.</t>
   </si>
   <si>
     <t xml:space="preserve">Worked examples: These document types illustrate reasoning. They are not actual archival discoveries.</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">Example</t>
   </si>
   <si>
-    <t xml:space="preserve">What do I claim?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What do I examine? (document type)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What can it establish?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What cannot it establish alone?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What else might explain it?</t>
+    <t xml:space="preserve">Claim under examination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document type examined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the source can establish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limits of the source alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possible rival explanation</t>
   </si>
   <si>
     <t xml:space="preserve">Lecture link</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">Local interpretations and existing opinions may differ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Your turn: Choose a case from the notes. Complete a yellow row. If you have not seen the document, write “document to locate”.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My case / week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My document / document to locate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What can I learn?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What remains unknown?</t>
+    <t xml:space="preserve">Exercise: Select a case from the lecture notes and complete a yellow row. Label any unexamined source “document to locate”.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case / week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document / document to locate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information established</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unresolved questions</t>
   </si>
   <si>
     <t xml:space="preserve">Rival explanation</t>
@@ -323,28 +323,28 @@
     <t xml:space="preserve">Practice 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Check yourself: Did I establish a document or an effect? If I claimed an effect, did I show the steps connecting them?</t>
+    <t xml:space="preserve">Review: Distinguish the existence of a document from evidence of an effect. Does any claim of influence identify the connecting steps?</t>
   </si>
   <si>
     <t xml:space="preserve">Basis: Week 6 on exchanges, week 7 on the CPI and week 11 on media. The example rows link to the relevant notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Separate reach from changes in support</t>
+    <t xml:space="preserve">Comparing reach and changes in support</t>
   </si>
   <si>
     <t xml:space="preserve">Entirely hypothetical data: A and B are fictional campaigns. These are not records of real people, students or historical events.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Look at the yellow inputs. 2. Read the worked example below. 3. Set D10 to 600 and watch the results.</t>
+    <t xml:space="preserve">1. Examine the yellow input cells. 2. Read the worked example below. 3. Set D10 to 600 and observe the resulting changes.</t>
   </si>
   <si>
     <t xml:space="preserve">In each initial example, the same 100 people selected from those reached answered the same support question before and after.</t>
   </si>
   <si>
-    <t xml:space="preserve">“Support” means a positive answer. Persuasion needs stronger evidence. This observation without a control group does not establish causation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A control group consists of similar people not receiving the campaign, observed for comparison. This example has no such group.</t>
+    <t xml:space="preserve">“Support” denotes a positive response. A claim of persuasion requires stronger evidence. Without a control group, this observation cannot establish causation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A control group consists of similar people who are not exposed to the campaign and are observed for comparison. This example includes no control group.</t>
   </si>
   <si>
     <t xml:space="preserve">Campaign</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">Change (percentage points)</t>
   </si>
   <si>
-    <t xml:space="preserve">How is it calculated?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How do I read it?</t>
+    <t xml:space="preserve">Calculation method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretation</t>
   </si>
   <si>
     <t xml:space="preserve">Reach = reached ÷ target.</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">Initial worked example: In A, 800 ÷ 1,000 = 80% reach. Support rises from 40% to 44%: 4 percentage points.</t>
   </si>
   <si>
-    <t xml:space="preserve">B starts with lower reach (40%) and a larger support increase (15 percentage points). Exposure and persuasion are separate questions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise 1: Change D10 from 800 to 600. Reach becomes 60%. Why does the change in support stay the same?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise 2: Change G10 from 44 to 60. Support becomes 60%, an increase of 20 percentage points. Which input changed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise 3: Clear E10. Why is a blank result more honest than displaying 0%? Then enter 100 again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise 4: What must you learn before saying “B persuaded more people”? Consider initial differences and other events.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your answer</t>
+    <t xml:space="preserve">B has lower initial reach (40%) and a larger increase in support (15 percentage points). Exposure and persuasion require separate assessment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise 1: Change D10 from 800 to 600. Reach becomes 60%. Explain why the change in support remains constant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise 2: Change G10 from 44 to 60. Support becomes 60%, an increase of 20 percentage points. Identify the input that changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise 3: Clear E10. Explain why a blank result represents missing data more accurately than 0%. Then restore the value 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise 4: Identify the additional evidence needed to claim that B persuaded more people. Consider initial differences and other events.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response</t>
   </si>
   <si>
     <t xml:space="preserve">What does reach measure?</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">What further data are needed?</t>
   </si>
   <si>
-    <t xml:space="preserve">Limit to my conclusion</t>
+    <t xml:space="preserve">Limit of the conclusion</t>
   </si>
   <si>
     <t xml:space="preserve">One-sentence conclusion</t>
   </si>
   <si>
-    <t xml:space="preserve">My explanation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click C16 to inspect its formula. D10/C10 in the formula bar means “people reached / people targeted”.</t>
+    <t xml:space="preserve">Analytical explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select C16 to inspect the formula. D10/C10 in the formula bar represents the ratio of people reached to people targeted.</t>
   </si>
   <si>
     <t xml:space="preserve">Percentage points: The difference between 40% and 44% is 4 points. The relative increase is 10%. These are different measures.</t>
@@ -452,28 +452,28 @@
     <t xml:space="preserve">Source: The numbers were constructed for teaching. Concepts draw on the course notes for weeks 1 and 14.</t>
   </si>
   <si>
-    <t xml:space="preserve">Read the concepts in everyday language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Find an unfamiliar term. 2. Read its everyday example. 3. Apply the final question to your course case.</t>
+    <t xml:space="preserve">Core concepts and illustrative analogies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Identify the concept to examine. 2. Read the illustrative example. 3. Apply the final question to the selected course case.</t>
   </si>
   <si>
     <t xml:space="preserve">Concept</t>
   </si>
   <si>
-    <t xml:space="preserve">Plain meaning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everyday analogy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask yourself</t>
+    <t xml:space="preserve">Concise definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative analogy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytical question</t>
   </si>
   <si>
     <t xml:space="preserve">Actor</t>
   </si>
   <si>
-    <t xml:space="preserve">A person or organisation trying to do something.</t>
+    <t xml:space="preserve">A person or organisation pursuing a particular objective.</t>
   </si>
   <si>
     <t xml:space="preserve">A café owner commissions an advert.</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">Students living near the café.</t>
   </si>
   <si>
-    <t xml:space="preserve">Which people? Am I treating them all as identical?</t>
+    <t xml:space="preserve">Which groups are examined? Are differences between them recognised?</t>
   </si>
   <si>
     <t xml:space="preserve">Resource</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">Mechanism</t>
   </si>
   <si>
-    <t xml:space="preserve">The process through which one thing may change another.</t>
+    <t xml:space="preserve">The process through which one factor may produce a change in another.</t>
   </si>
   <si>
     <t xml:space="preserve">A trusted recommendation encourages a trial.</t>
   </si>
   <si>
-    <t xml:space="preserve">What is the intermediate step? Can I observe it?</t>
+    <t xml:space="preserve">What is the intermediate step, and can it be observed?</t>
   </si>
   <si>
     <t xml:space="preserve">Reach</t>
   </si>
   <si>
-    <t xml:space="preserve">People encountering content. Specify the definition and counting method.</t>
+    <t xml:space="preserve">People’s exposure to content. The definition and counting method must be specified.</t>
   </si>
   <si>
     <t xml:space="preserve">How many people actually saw the advert?</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">How people understand and assess a message.</t>
   </si>
   <si>
-    <t xml:space="preserve">One person finds the advert useful, another off-putting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What meaning did the audience make? Can I hear its own voice?</t>
+    <t xml:space="preserve">The same advertisement is perceived as useful by one person and unappealing by another.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How did the audience interpret the message? Is evidence of its own account available?</t>
   </si>
   <si>
     <t xml:space="preserve">Attitude and behaviour</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">Liking the café is an attitude; buying is behaviour.</t>
   </si>
   <si>
-    <t xml:space="preserve">Am I measuring a view or an action?</t>
+    <t xml:space="preserve">Does the measure concern an evaluation or an observable action?</t>
   </si>
   <si>
     <t xml:space="preserve">Hard power</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">Following someone because they set an appealing example.</t>
   </si>
   <si>
-    <t xml:space="preserve">Am I confusing admiration with policy support?</t>
+    <t xml:space="preserve">Are admiration and support for a policy analytically distinguished?</t>
   </si>
   <si>
     <t xml:space="preserve">Public diplomacy</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">A speaker who openly corrects an error.</t>
   </si>
   <si>
-    <t xml:space="preserve">How do I know why people believe the source?</t>
+    <t xml:space="preserve">What evidence explains why the source is trusted?</t>
   </si>
   <si>
     <t xml:space="preserve">Reciprocity</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">A move from 40% to 44% is 4 percentage points.</t>
   </si>
   <si>
-    <t xml:space="preserve">Am I confusing this with a relative percentage increase?</t>
+    <t xml:space="preserve">Are percentage points distinguished from relative percentage increases?</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Conceptual explanations in the English course notes. Everyday analogies serve only to support learning.</t>
   </si>
   <si>
-    <t xml:space="preserve">Build your research design step by step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Read the fictional worked example. 2. Write your own case in the yellow column. 3. Also seek evidence against your claim.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source provenance identifies who created a document, when, for what purpose, and how it reached you.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An observation is what appears in the record. An interpretation is what you infer. Keeping them separate makes your reasoning auditable.</t>
+    <t xml:space="preserve">Stages of research design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Examine the fictional worked example. 2. Describe the selected case in the yellow column. 3. Seek evidence that may challenge the claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source provenance identifies a document’s creator, date, purpose and route of transmission to the researcher.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An observation concerns what appears in the record. An interpretation is an inference from it. Recording them separately makes the reasoning open to scrutiny.</t>
   </si>
   <si>
     <t xml:space="preserve">The example is entirely fictional. EXAMPLE-1 is not a real record identifier. Do not enter student names or personal data in the yellow cells.</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">Fictional worked example</t>
   </si>
   <si>
-    <t xml:space="preserve">Your study (complete this)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim: the statement I test</t>
+    <t xml:space="preserve">Research application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim: statement to be tested</t>
   </si>
   <si>
     <t xml:space="preserve">The exchange workshop contributed to two teachers preparing their first joint lesson plan. This is the claim to test, not an established result.</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">EXAMPLE-1: An imagined private letter from participant A to participant B after the workshop. A real study must verify creator, recipient, date, purpose and repository.</t>
   </si>
   <si>
-    <t xml:space="preserve">Observation: what exactly is in the record?</t>
+    <t xml:space="preserve">Observation: content of the record</t>
   </si>
   <si>
     <t xml:space="preserve">The imagined letter mentions a joint lesson draft. This observation concerns the letter’s content; it does not show that the draft was implemented.</t>
   </si>
   <si>
-    <t xml:space="preserve">Interpretation: what do I infer?</t>
+    <t xml:space="preserve">Interpretation: inference from the observation</t>
   </si>
   <si>
     <t xml:space="preserve">It is consistent with continued contact after the workshop. It does not establish that the workshop was the sole cause or that the relationship endured.</t>
@@ -740,28 +740,28 @@
     <t xml:space="preserve">The teachers may have known each other or already planned another joint project. Pre-workshop correspondence could test this explanation.</t>
   </si>
   <si>
-    <t xml:space="preserve">Limitation: what are the limits of my evidence?</t>
+    <t xml:space="preserve">Limitation: scope of the evidence</t>
   </si>
   <si>
     <t xml:space="preserve">It relies on one self-report. Selective survival, positive self-presentation and the other party’s silence may distort the account. Contact is not a policy change.</t>
   </si>
   <si>
-    <t xml:space="preserve">Next evidence: what will I check?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare earlier records, the second participant’s account and the dated joint draft. Narrow the claim if they conflict; repeated use of one source is not independent corroboration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Now specify the design: Each row makes a research choice explicit. If data are absent, state what to seek rather than invent a result.</t>
+    <t xml:space="preserve">Further evidence: matters to verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare earlier records, the second participant’s account and the dated joint draft. Conflicting evidence requires a narrower claim. Repetition of one source is not independent corroboration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design decisions: Each row specifies a research choice. Where data are absent, identify the evidence required and limit the conclusion accordingly.</t>
   </si>
   <si>
     <t xml:space="preserve">Design decision</t>
   </si>
   <si>
-    <t xml:space="preserve">How the example applies it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My research plan</t>
+    <t xml:space="preserve">Application in the example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research plan</t>
   </si>
   <si>
     <t xml:space="preserve">Research question</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">Unit of analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">One pair of teachers and its collaborative process. Do not mix claims about individuals, events and countries.</t>
+    <t xml:space="preserve">One pair of teachers and its collaborative process. Claims about individuals, events and countries remain analytically distinct.</t>
   </si>
   <si>
     <t xml:space="preserve">Time and scope</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">Case selection</t>
   </si>
   <si>
-    <t xml:space="preserve">Do not select only success stories. Seek contacts that did not continue and record why people or documents were excluded.</t>
+    <t xml:space="preserve">Case selection extends beyond accounts of success. Investigate contacts that did not continue and document why people or records were excluded.</t>
   </si>
   <si>
     <t xml:space="preserve">Comparison and counterfactual</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">Record author, date, title, collection or publication, record/page and access details. Keep a short log of translations, missing records and revised interpretations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Before submission: Are claim, observation, interpretation and limitation separate? What evidence would test the strongest rival explanation?</t>
+    <t xml:space="preserve">Review before submission: Are the claim, observation, interpretation and limitation distinguished? What evidence would test the strongest rival explanation?</t>
   </si>
   <si>
     <t xml:space="preserve">Course basis: Week 6 on exchanges and week 14 on evidence and evaluation. This fictional example establishes no historical finding.</t>
@@ -1481,11 +1481,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="12972810"/>
-        <c:axId val="99939787"/>
+        <c:axId val="23604262"/>
+        <c:axId val="30397006"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="12972810"/>
+        <c:axId val="23604262"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1530,7 +1530,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99939787"/>
+        <c:crossAx val="30397006"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1538,7 +1538,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99939787"/>
+        <c:axId val="30397006"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1583,7 +1583,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12972810"/>
+        <c:crossAx val="23604262"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
